--- a/Team-Data/2007-08/1-3-2007-08.xlsx
+++ b/Team-Data/2007-08/1-3-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE2" t="n">
         <v>14</v>
@@ -751,7 +818,7 @@
         <v>14</v>
       </c>
       <c r="AH2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI2" t="n">
         <v>28</v>
@@ -760,7 +827,7 @@
         <v>27</v>
       </c>
       <c r="AK2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL2" t="n">
         <v>29</v>
@@ -787,7 +854,7 @@
         <v>24</v>
       </c>
       <c r="AT2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU2" t="n">
         <v>23</v>
@@ -802,7 +869,7 @@
         <v>6</v>
       </c>
       <c r="AY2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ2" t="n">
         <v>18</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>13.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -933,10 +1000,10 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -969,7 +1036,7 @@
         <v>7</v>
       </c>
       <c r="AT3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU3" t="n">
         <v>9</v>
@@ -984,7 +1051,7 @@
         <v>26</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>14</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -1103,31 +1170,31 @@
         <v>-5.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE4" t="n">
         <v>24</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG4" t="n">
         <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="n">
         <v>27</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK4" t="n">
         <v>20</v>
       </c>
       <c r="AL4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM4" t="n">
         <v>15</v>
@@ -1136,7 +1203,7 @@
         <v>5</v>
       </c>
       <c r="AO4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP4" t="n">
         <v>13</v>
@@ -1151,7 +1218,7 @@
         <v>29</v>
       </c>
       <c r="AT4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU4" t="n">
         <v>21</v>
@@ -1175,7 +1242,7 @@
         <v>14</v>
       </c>
       <c r="BB4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC4" t="n">
         <v>26</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -1207,67 +1274,67 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5" t="n">
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>0.387</v>
+        <v>0.4</v>
       </c>
       <c r="H5" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="I5" t="n">
-        <v>35.8</v>
+        <v>35.5</v>
       </c>
       <c r="J5" t="n">
-        <v>85.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="K5" t="n">
         <v>0.419</v>
       </c>
       <c r="L5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="M5" t="n">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.327</v>
+        <v>0.335</v>
       </c>
       <c r="O5" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P5" t="n">
         <v>22.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.762</v>
+        <v>0.76</v>
       </c>
       <c r="R5" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="S5" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T5" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U5" t="n">
         <v>21.7</v>
       </c>
       <c r="V5" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W5" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
         <v>5.9</v>
@@ -1279,31 +1346,31 @@
         <v>20.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.8</v>
+        <v>93.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.5</v>
+        <v>-3.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
       </c>
       <c r="AF5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI5" t="n">
         <v>22</v>
       </c>
-      <c r="AG5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>20</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AK5" t="n">
         <v>29</v>
@@ -1315,7 +1382,7 @@
         <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO5" t="n">
         <v>23</v>
@@ -1324,7 +1391,7 @@
         <v>25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
@@ -1342,25 +1409,25 @@
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY5" t="n">
         <v>27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA5" t="n">
         <v>19</v>
       </c>
       <c r="BB5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
         <v>14</v>
@@ -1479,7 +1546,7 @@
         <v>17</v>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
         <v>23</v>
@@ -1491,7 +1558,7 @@
         <v>26</v>
       </c>
       <c r="AL6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM6" t="n">
         <v>13</v>
@@ -1530,7 +1597,7 @@
         <v>21</v>
       </c>
       <c r="AY6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ6" t="n">
         <v>24</v>
@@ -1542,7 +1609,7 @@
         <v>19</v>
       </c>
       <c r="BC6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>4</v>
       </c>
       <c r="AD7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
         <v>5</v>
@@ -1661,13 +1728,13 @@
         <v>5</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
         <v>15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK7" t="n">
         <v>6</v>
@@ -1694,13 +1761,13 @@
         <v>21</v>
       </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT7" t="n">
         <v>15</v>
       </c>
       <c r="AU7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV7" t="n">
         <v>5</v>
@@ -1709,7 +1776,7 @@
         <v>28</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY7" t="n">
         <v>6</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -1753,88 +1820,88 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F8" t="n">
         <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0.613</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="n">
         <v>48.3</v>
       </c>
       <c r="I8" t="n">
-        <v>38.5</v>
+        <v>38.7</v>
       </c>
       <c r="J8" t="n">
-        <v>84.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="K8" t="n">
-        <v>0.454</v>
+        <v>0.456</v>
       </c>
       <c r="L8" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M8" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0.335</v>
+        <v>0.336</v>
       </c>
       <c r="O8" t="n">
-        <v>22.9</v>
+        <v>23.2</v>
       </c>
       <c r="P8" t="n">
-        <v>30.4</v>
+        <v>30.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
       <c r="R8" t="n">
         <v>11.5</v>
       </c>
       <c r="S8" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="T8" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="U8" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="V8" t="n">
         <v>16.5</v>
       </c>
       <c r="W8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>106.1</v>
+        <v>106.9</v>
       </c>
       <c r="AC8" t="n">
         <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF8" t="n">
         <v>8</v>
@@ -1843,22 +1910,22 @@
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AI8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AK8" t="n">
         <v>12</v>
       </c>
       <c r="AL8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN8" t="n">
         <v>24</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR8" t="n">
         <v>14</v>
@@ -1885,7 +1952,7 @@
         <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1894,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="AY8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ8" t="n">
         <v>19</v>
@@ -1903,7 +1970,7 @@
         <v>1</v>
       </c>
       <c r="BB8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>10.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2031,7 +2098,7 @@
         <v>8</v>
       </c>
       <c r="AJ9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK9" t="n">
         <v>4</v>
@@ -2073,16 +2140,16 @@
         <v>19</v>
       </c>
       <c r="AX9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ9" t="n">
         <v>9</v>
       </c>
       <c r="BA9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB9" t="n">
         <v>11</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2265,7 @@
         <v>3</v>
       </c>
       <c r="AE10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF10" t="n">
         <v>11</v>
@@ -2207,7 +2274,7 @@
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>0.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>14</v>
@@ -2392,7 +2459,7 @@
         <v>17</v>
       </c>
       <c r="AI11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ11" t="n">
         <v>11</v>
@@ -2407,7 +2474,7 @@
         <v>8</v>
       </c>
       <c r="AN11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO11" t="n">
         <v>27</v>
@@ -2428,7 +2495,7 @@
         <v>5</v>
       </c>
       <c r="AU11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV11" t="n">
         <v>12</v>
@@ -2446,7 +2513,7 @@
         <v>10</v>
       </c>
       <c r="BA11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB11" t="n">
         <v>21</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2638,7 @@
         <v>19</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
         <v>6</v>
@@ -2580,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL12" t="n">
         <v>5</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO12" t="n">
         <v>19</v>
@@ -2604,7 +2671,7 @@
         <v>11</v>
       </c>
       <c r="AS12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
         <v>4</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2765,7 +2832,7 @@
         <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM13" t="n">
         <v>25</v>
@@ -2783,7 +2850,7 @@
         <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS13" t="n">
         <v>8</v>
@@ -2801,7 +2868,7 @@
         <v>22</v>
       </c>
       <c r="AX13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>4.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF14" t="n">
         <v>5</v>
@@ -2938,7 +3005,7 @@
         <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
         <v>10</v>
@@ -2983,7 +3050,7 @@
         <v>5</v>
       </c>
       <c r="AX14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY14" t="n">
         <v>11</v>
@@ -2995,7 +3062,7 @@
         <v>5</v>
       </c>
       <c r="BB14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3120,7 +3187,7 @@
         <v>15</v>
       </c>
       <c r="AI15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ15" t="n">
         <v>17</v>
@@ -3144,7 +3211,7 @@
         <v>18</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
         <v>27</v>
@@ -3153,7 +3220,7 @@
         <v>12</v>
       </c>
       <c r="AT15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU15" t="n">
         <v>20</v>
@@ -3168,7 +3235,7 @@
         <v>12</v>
       </c>
       <c r="AY15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ15" t="n">
         <v>5</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
         <v>28</v>
@@ -3299,7 +3366,7 @@
         <v>29</v>
       </c>
       <c r="AH16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI16" t="n">
         <v>24</v>
@@ -3308,7 +3375,7 @@
         <v>28</v>
       </c>
       <c r="AK16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL16" t="n">
         <v>27</v>
@@ -3332,7 +3399,7 @@
         <v>28</v>
       </c>
       <c r="AS16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT16" t="n">
         <v>30</v>
@@ -3347,13 +3414,13 @@
         <v>8</v>
       </c>
       <c r="AX16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA16" t="n">
         <v>9</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -3469,19 +3536,19 @@
         <v>-5.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE17" t="n">
         <v>21</v>
       </c>
       <c r="AF17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI17" t="n">
         <v>16</v>
@@ -3502,7 +3569,7 @@
         <v>20</v>
       </c>
       <c r="AO17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP17" t="n">
         <v>23</v>
@@ -3526,7 +3593,7 @@
         <v>22</v>
       </c>
       <c r="AW17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX17" t="n">
         <v>18</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE19" t="n">
         <v>14</v>
@@ -3845,7 +3912,7 @@
         <v>16</v>
       </c>
       <c r="AH19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>4</v>
       </c>
       <c r="AD20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
         <v>5</v>
@@ -4027,7 +4094,7 @@
         <v>5</v>
       </c>
       <c r="AH20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI20" t="n">
         <v>14</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE21" t="n">
         <v>28</v>
@@ -4209,7 +4276,7 @@
         <v>28</v>
       </c>
       <c r="AH21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI21" t="n">
         <v>26</v>
@@ -4260,7 +4327,7 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ21" t="n">
         <v>20</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF22" t="n">
         <v>8</v>
@@ -4391,13 +4458,13 @@
         <v>7</v>
       </c>
       <c r="AH22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK22" t="n">
         <v>8</v>
@@ -4430,7 +4497,7 @@
         <v>9</v>
       </c>
       <c r="AU22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV22" t="n">
         <v>16</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-0.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>20</v>
@@ -4576,7 +4643,7 @@
         <v>17</v>
       </c>
       <c r="AI23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="n">
         <v>22</v>
@@ -4591,7 +4658,7 @@
         <v>28</v>
       </c>
       <c r="AN23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO23" t="n">
         <v>22</v>
@@ -4609,7 +4676,7 @@
         <v>23</v>
       </c>
       <c r="AT23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU23" t="n">
         <v>24</v>
@@ -4633,7 +4700,7 @@
         <v>20</v>
       </c>
       <c r="BB23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC23" t="n">
         <v>17</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -4665,61 +4732,61 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F24" t="n">
         <v>9</v>
       </c>
       <c r="G24" t="n">
-        <v>0.719</v>
+        <v>0.71</v>
       </c>
       <c r="H24" t="n">
         <v>48</v>
       </c>
       <c r="I24" t="n">
-        <v>41.9</v>
+        <v>42.1</v>
       </c>
       <c r="J24" t="n">
-        <v>85.3</v>
+        <v>85.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.491</v>
+        <v>0.492</v>
       </c>
       <c r="L24" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="N24" t="n">
         <v>0.37</v>
       </c>
       <c r="O24" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="P24" t="n">
-        <v>22.3</v>
+        <v>21.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.769</v>
+        <v>0.773</v>
       </c>
       <c r="R24" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="T24" t="n">
-        <v>41.4</v>
+        <v>41.1</v>
       </c>
       <c r="U24" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="V24" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W24" t="n">
         <v>7.5</v>
@@ -4728,31 +4795,31 @@
         <v>6.8</v>
       </c>
       <c r="Y24" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z24" t="n">
         <v>19</v>
       </c>
       <c r="AA24" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>109.2</v>
+        <v>109.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
       </c>
       <c r="AF24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH24" t="n">
         <v>24</v>
@@ -4761,7 +4828,7 @@
         <v>1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK24" t="n">
         <v>1</v>
@@ -4776,22 +4843,22 @@
         <v>7</v>
       </c>
       <c r="AO24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP24" t="n">
         <v>26</v>
       </c>
       <c r="AQ24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR24" t="n">
         <v>30</v>
       </c>
       <c r="AS24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4800,7 +4867,7 @@
         <v>6</v>
       </c>
       <c r="AW24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -4847,61 +4914,61 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F25" t="n">
         <v>13</v>
       </c>
       <c r="G25" t="n">
-        <v>0.606</v>
+        <v>0.594</v>
       </c>
       <c r="H25" t="n">
-        <v>48.5</v>
+        <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J25" t="n">
-        <v>77.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="K25" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L25" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="M25" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="N25" t="n">
-        <v>0.383</v>
+        <v>0.378</v>
       </c>
       <c r="O25" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P25" t="n">
         <v>23.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.757</v>
+        <v>0.753</v>
       </c>
       <c r="R25" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="S25" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="T25" t="n">
-        <v>39.9</v>
+        <v>39.6</v>
       </c>
       <c r="U25" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V25" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W25" t="n">
         <v>5.5</v>
@@ -4910,7 +4977,7 @@
         <v>4.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Z25" t="n">
         <v>19.9</v>
@@ -4919,13 +4986,13 @@
         <v>21.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>96.40000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>8</v>
@@ -4937,19 +5004,19 @@
         <v>10</v>
       </c>
       <c r="AH25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK25" t="n">
         <v>9</v>
       </c>
-      <c r="AI25" t="n">
-        <v>18</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>10</v>
-      </c>
       <c r="AL25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AM25" t="n">
         <v>16</v>
@@ -4961,19 +5028,19 @@
         <v>21</v>
       </c>
       <c r="AP25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS25" t="n">
         <v>21</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>20</v>
-      </c>
       <c r="AT25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU25" t="n">
         <v>13</v>
@@ -4988,13 +5055,13 @@
         <v>19</v>
       </c>
       <c r="AY25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ25" t="n">
         <v>6</v>
       </c>
       <c r="BA25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB25" t="n">
         <v>18</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-3.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="n">
         <v>21</v>
@@ -5119,7 +5186,7 @@
         <v>21</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
         <v>25</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -5211,85 +5278,85 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E27" t="n">
         <v>21</v>
       </c>
       <c r="F27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7</v>
+        <v>0.724</v>
       </c>
       <c r="H27" t="n">
         <v>48</v>
       </c>
       <c r="I27" t="n">
-        <v>36.7</v>
+        <v>37.1</v>
       </c>
       <c r="J27" t="n">
-        <v>79.3</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.463</v>
+        <v>0.466</v>
       </c>
       <c r="L27" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.389</v>
+        <v>0.39</v>
       </c>
       <c r="O27" t="n">
         <v>16.6</v>
       </c>
       <c r="P27" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.757</v>
+        <v>0.762</v>
       </c>
       <c r="R27" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="S27" t="n">
         <v>31.8</v>
       </c>
       <c r="T27" t="n">
-        <v>41.7</v>
+        <v>41.9</v>
       </c>
       <c r="U27" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="V27" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="W27" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="X27" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AA27" t="n">
         <v>20</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.2</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="AD27" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AE27" t="n">
         <v>5</v>
@@ -5298,16 +5365,16 @@
         <v>3</v>
       </c>
       <c r="AG27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH27" t="n">
         <v>24</v>
       </c>
       <c r="AI27" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AJ27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK27" t="n">
         <v>7</v>
@@ -5328,16 +5395,16 @@
         <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AU27" t="n">
         <v>10</v>
@@ -5352,7 +5419,7 @@
         <v>29</v>
       </c>
       <c r="AY27" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ27" t="n">
         <v>1</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -5393,124 +5460,124 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E28" t="n">
         <v>9</v>
       </c>
       <c r="F28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G28" t="n">
-        <v>0.281</v>
+        <v>0.29</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J28" t="n">
-        <v>85.3</v>
+        <v>84.7</v>
       </c>
       <c r="K28" t="n">
-        <v>0.44</v>
+        <v>0.442</v>
       </c>
       <c r="L28" t="n">
         <v>4.8</v>
       </c>
       <c r="M28" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="O28" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="P28" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="Q28" t="n">
         <v>0.769</v>
       </c>
       <c r="R28" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="S28" t="n">
         <v>33.5</v>
       </c>
       <c r="T28" t="n">
-        <v>45.3</v>
+        <v>45.1</v>
       </c>
       <c r="U28" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V28" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="W28" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="AA28" t="n">
         <v>20.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>-6.3</v>
+        <v>-6.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AE28" t="n">
         <v>26</v>
       </c>
       <c r="AF28" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI28" t="n">
         <v>7</v>
       </c>
       <c r="AJ28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK28" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM28" t="n">
         <v>26</v>
       </c>
       <c r="AN28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR28" t="n">
         <v>13</v>
@@ -5522,25 +5589,25 @@
         <v>1</v>
       </c>
       <c r="AU28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AV28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AY28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ28" t="n">
         <v>15</v>
       </c>
       <c r="BA28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB28" t="n">
         <v>14</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>1.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
         <v>13</v>
@@ -5665,10 +5732,10 @@
         <v>12</v>
       </c>
       <c r="AH29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ29" t="n">
         <v>8</v>
@@ -5716,7 +5783,7 @@
         <v>24</v>
       </c>
       <c r="AY29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ29" t="n">
         <v>7</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF30" t="n">
         <v>15</v>
@@ -5865,7 +5932,7 @@
         <v>30</v>
       </c>
       <c r="AN30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>1.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6029,10 +6096,10 @@
         <v>15</v>
       </c>
       <c r="AH31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ31" t="n">
         <v>12</v>
@@ -6041,7 +6108,7 @@
         <v>14</v>
       </c>
       <c r="AL31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM31" t="n">
         <v>11</v>
@@ -6077,7 +6144,7 @@
         <v>17</v>
       </c>
       <c r="AX31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-3-2007-08</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
